--- a/data/polvozrast_opora_march26.xlsx
+++ b/data/polvozrast_opora_march26.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\ВайбКодинг\Ai Coder\Programm Ai Coder\.aicoder\Projects\yandex-direct-analytic-datas-project\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C14567-120E-4E85-9566-D30C737B2805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="43">
   <si>
     <t>Клиент: Болотов Артем Игоревич (avtourist-novosib)</t>
   </si>
@@ -146,24 +154,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10.0"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
-      <sz val="10.0"/>
-      <b val="true"/>
     </font>
   </fonts>
   <fills count="2">
@@ -171,7 +178,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -188,50 +195,376 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+  <a:themeElements>
+    <a:clrScheme name="Стандартная">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Стандартная">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Стандартная">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O156"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.0" customWidth="true"/>
-    <col min="2" max="2" width="11.0" customWidth="true"/>
-    <col min="3" max="3" width="13.0" customWidth="true"/>
-    <col min="4" max="4" width="13.0" customWidth="true"/>
-    <col min="5" max="5" width="10.0" customWidth="true"/>
-    <col min="6" max="6" width="9.0" customWidth="true"/>
-    <col min="7" max="7" width="8.0" customWidth="true"/>
-    <col min="8" max="8" width="10.0" customWidth="true"/>
-    <col min="9" max="9" width="10.0" customWidth="true"/>
-    <col min="10" max="10" width="18.0" customWidth="true"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -262,8 +595,11 @@
       <c r="J5" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="O5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -276,26 +612,29 @@
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="1">
         <v>522252.63</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>501311.0</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>10660.0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>238.0</v>
-      </c>
-      <c r="I6" s="1" t="n">
+      <c r="F6" s="1">
+        <v>501311</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10660</v>
+      </c>
+      <c r="H6" s="1">
+        <v>238</v>
+      </c>
+      <c r="I6" s="1">
         <v>36.21</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="1">
         <v>1.04</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="O6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -308,26 +647,29 @@
       <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="1">
         <v>53988.08</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>535.0</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="I7" s="1" t="n">
+      <c r="F7" s="1">
+        <v>535</v>
+      </c>
+      <c r="G7" s="1">
+        <v>31</v>
+      </c>
+      <c r="H7" s="1">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1">
         <v>28.57</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -340,26 +682,29 @@
       <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="1">
         <v>50224.23</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>347.0</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="I8" s="1" t="n">
+      <c r="F8" s="1">
+        <v>347</v>
+      </c>
+      <c r="G8" s="1">
+        <v>36</v>
+      </c>
+      <c r="H8" s="1">
+        <v>14</v>
+      </c>
+      <c r="I8" s="1">
         <v>17.5</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="1">
         <v>1.05</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="O8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -372,26 +717,29 @@
       <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="1">
         <v>43304.98</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>536.0</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="I9" s="1" t="n">
+      <c r="F9" s="1">
+        <v>536</v>
+      </c>
+      <c r="G9" s="1">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1">
+        <v>16</v>
+      </c>
+      <c r="I9" s="1">
         <v>15.63</v>
       </c>
-      <c r="J9" s="1" t="n">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="J9" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -404,26 +752,29 @@
       <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="1">
         <v>33671.26</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>298.0</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I10" s="1" t="n">
+      <c r="F10" s="1">
+        <v>298</v>
+      </c>
+      <c r="G10" s="1">
+        <v>27</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4</v>
+      </c>
+      <c r="I10" s="1">
         <v>35.71</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="1">
         <v>1.04</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="O10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -436,26 +787,29 @@
       <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="1">
         <v>25314.11</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>298.0</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11" s="1">
+        <v>298</v>
+      </c>
+      <c r="G11" s="1">
+        <v>21</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>36.840000000000003</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -468,26 +822,29 @@
       <c r="D12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="1">
         <v>23214.74</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>164.0</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="I12" s="1" t="n">
+      <c r="F12" s="1">
+        <v>164</v>
+      </c>
+      <c r="G12" s="1">
+        <v>17</v>
+      </c>
+      <c r="H12" s="1">
+        <v>8</v>
+      </c>
+      <c r="I12" s="1">
         <v>37.5</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -500,26 +857,29 @@
       <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>20182.94</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>463.0</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>22.0</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>18.33</v>
-      </c>
-      <c r="J13" s="1" t="n">
+      <c r="E13" s="1">
+        <v>20182.939999999999</v>
+      </c>
+      <c r="F13" s="1">
+        <v>463</v>
+      </c>
+      <c r="G13" s="1">
+        <v>57</v>
+      </c>
+      <c r="H13" s="1">
+        <v>22</v>
+      </c>
+      <c r="I13" s="1">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="J13" s="1">
         <v>1.35</v>
       </c>
-    </row>
-    <row r="14">
+      <c r="O13" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -532,26 +892,29 @@
       <c r="D14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="1">
         <v>17565.78</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>564.0</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J14" s="1" t="n">
+      <c r="F14" s="1">
+        <v>564</v>
+      </c>
+      <c r="G14" s="1">
+        <v>49</v>
+      </c>
+      <c r="H14" s="1">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1">
+        <v>25</v>
+      </c>
+      <c r="J14" s="1">
         <v>1.23</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="O14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
@@ -564,26 +927,26 @@
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="1">
         <v>15935.29</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>153.0</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I15" s="1" t="n">
+      <c r="F15" s="1">
+        <v>153</v>
+      </c>
+      <c r="G15" s="1">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="1">
         <v>22.22</v>
       </c>
-      <c r="J15" s="1" t="n">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="J15" s="1">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -596,26 +959,26 @@
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="1">
         <v>11566.71</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>214.0</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="I16" s="1" t="n">
+      <c r="F16" s="1">
+        <v>214</v>
+      </c>
+      <c r="G16" s="1">
+        <v>23</v>
+      </c>
+      <c r="H16" s="1">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1">
         <v>27.59</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="1">
         <v>1.34</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -628,26 +991,26 @@
       <c r="D17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="1">
         <v>11285.9</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>160.0</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17" s="1">
+        <v>160</v>
+      </c>
+      <c r="G17" s="1">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -660,26 +1023,26 @@
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>10186.8</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>251.0</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I18" s="1" t="n">
+      <c r="E18" s="1">
+        <v>10186.799999999999</v>
+      </c>
+      <c r="F18" s="1">
+        <v>251</v>
+      </c>
+      <c r="G18" s="1">
+        <v>20</v>
+      </c>
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1">
         <v>19.05</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="1">
         <v>1.29</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>15</v>
       </c>
@@ -692,26 +1055,26 @@
       <c r="D19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="1">
         <v>10003.25</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>184.0</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I19" s="1" t="n">
+      <c r="F19" s="1">
+        <v>184</v>
+      </c>
+      <c r="G19" s="1">
+        <v>8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
         <v>33.33</v>
       </c>
-      <c r="J19" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -724,26 +1087,26 @@
       <c r="D20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="1">
         <v>8273.36</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>27252.0</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>683.0</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="I20" s="1" t="n">
+      <c r="F20" s="1">
+        <v>27252</v>
+      </c>
+      <c r="G20" s="1">
+        <v>683</v>
+      </c>
+      <c r="H20" s="1">
+        <v>10</v>
+      </c>
+      <c r="I20" s="1">
         <v>42.37</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="1">
         <v>1.04</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -756,26 +1119,26 @@
       <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="1">
         <v>8111.66</v>
       </c>
-      <c r="F21" s="1" t="n">
-        <v>343.0</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I21" s="1" t="n">
+      <c r="F21" s="1">
+        <v>343</v>
+      </c>
+      <c r="G21" s="1">
+        <v>30</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
         <v>22.58</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="1">
         <v>1.65</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -788,26 +1151,26 @@
       <c r="D22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="1">
         <v>7558.6</v>
       </c>
-      <c r="F22" s="1" t="n">
-        <v>23618.0</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>852.0</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="I22" s="1" t="n">
+      <c r="F22" s="1">
+        <v>23618</v>
+      </c>
+      <c r="G22" s="1">
+        <v>852</v>
+      </c>
+      <c r="H22" s="1">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1">
         <v>42.9</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -820,26 +1183,26 @@
       <c r="D23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="1">
         <v>7342.49</v>
       </c>
-      <c r="F23" s="1" t="n">
-        <v>355.0</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J23" s="1" t="n">
+      <c r="F23" s="1">
+        <v>355</v>
+      </c>
+      <c r="G23" s="1">
+        <v>30</v>
+      </c>
+      <c r="H23" s="1">
+        <v>7</v>
+      </c>
+      <c r="I23" s="1">
+        <v>25</v>
+      </c>
+      <c r="J23" s="1">
         <v>1.5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -852,26 +1215,26 @@
       <c r="D24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="1">
         <v>6819.72</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>349.0</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="J24" s="1" t="n">
+      <c r="F24" s="1">
+        <v>349</v>
+      </c>
+      <c r="G24" s="1">
+        <v>28</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="1">
+        <v>34.479999999999997</v>
+      </c>
+      <c r="J24" s="1">
         <v>1.38</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
@@ -884,26 +1247,26 @@
       <c r="D25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="1">
         <v>6470.34</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>311.0</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="I25" s="1" t="n">
+      <c r="F25" s="1">
+        <v>311</v>
+      </c>
+      <c r="G25" s="1">
+        <v>18</v>
+      </c>
+      <c r="H25" s="1">
+        <v>13</v>
+      </c>
+      <c r="I25" s="1">
         <v>29.17</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="1">
         <v>1.42</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>15</v>
       </c>
@@ -916,26 +1279,26 @@
       <c r="D26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="1">
         <v>6157.92</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>501.0</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="1" t="n">
+      <c r="F26" s="1">
+        <v>501</v>
+      </c>
+      <c r="G26" s="1">
+        <v>8</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
         <v>66.67</v>
       </c>
-      <c r="J26" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
@@ -948,26 +1311,26 @@
       <c r="D27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="1">
         <v>5968.08</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>266.0</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I27" s="1" t="n">
+      <c r="F27" s="1">
+        <v>266</v>
+      </c>
+      <c r="G27" s="1">
+        <v>19</v>
+      </c>
+      <c r="H27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1">
         <v>15.79</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="1">
         <v>2.11</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
@@ -980,26 +1343,26 @@
       <c r="D28" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="1">
         <v>5553.95</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>46.0</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I28" s="1" t="n">
+      <c r="F28" s="1">
+        <v>46</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1">
         <v>66.67</v>
       </c>
-      <c r="J28" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1012,26 +1375,26 @@
       <c r="D29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="1">
         <v>5300.71</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>260.0</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I29" s="1" t="n">
+      <c r="F29" s="1">
+        <v>260</v>
+      </c>
+      <c r="G29" s="1">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
         <v>22.22</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="1">
         <v>1.33</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -1044,26 +1407,26 @@
       <c r="D30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="1">
         <v>5219.13</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>24743.0</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>1168.0</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I30" s="1" t="n">
+      <c r="F30" s="1">
+        <v>24743</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1168</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1">
         <v>40.93</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="1">
         <v>1.02</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1076,26 +1439,26 @@
       <c r="D31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>5192.36</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>250.0</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="J31" s="1" t="n">
+      <c r="E31" s="1">
+        <v>5192.3599999999997</v>
+      </c>
+      <c r="F31" s="1">
+        <v>250</v>
+      </c>
+      <c r="G31" s="1">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="J31" s="1">
         <v>1.08</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
@@ -1108,26 +1471,26 @@
       <c r="D32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="1">
         <v>5179.2</v>
       </c>
-      <c r="F32" s="1" t="n">
-        <v>215.0</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="I32" s="1" t="n">
+      <c r="F32" s="1">
+        <v>215</v>
+      </c>
+      <c r="G32" s="1">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1">
+        <v>5</v>
+      </c>
+      <c r="I32" s="1">
         <v>18.18</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="1">
         <v>1.32</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1140,26 +1503,26 @@
       <c r="D33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>5125.06</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>19990.0</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>739.0</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I33" s="1" t="n">
+      <c r="E33" s="1">
+        <v>5125.0600000000004</v>
+      </c>
+      <c r="F33" s="1">
+        <v>19990</v>
+      </c>
+      <c r="G33" s="1">
+        <v>739</v>
+      </c>
+      <c r="H33" s="1">
+        <v>4</v>
+      </c>
+      <c r="I33" s="1">
         <v>36.97</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="1">
         <v>1.02</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>26</v>
       </c>
@@ -1172,26 +1535,26 @@
       <c r="D34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="1">
         <v>4956.82</v>
       </c>
-      <c r="F34" s="1" t="n">
-        <v>144.0</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I34" s="1" t="n">
+      <c r="F34" s="1">
+        <v>144</v>
+      </c>
+      <c r="G34" s="1">
+        <v>12</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
         <v>6.67</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="1">
         <v>1.47</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1204,26 +1567,26 @@
       <c r="D35" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="1">
         <v>4915.71</v>
       </c>
-      <c r="F35" s="1" t="n">
-        <v>212.0</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I35" s="1" t="n">
+      <c r="F35" s="1">
+        <v>212</v>
+      </c>
+      <c r="G35" s="1">
+        <v>8</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
         <v>22.22</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="1">
         <v>1.44</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>26</v>
       </c>
@@ -1236,26 +1599,26 @@
       <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="1">
         <v>4391.87</v>
       </c>
-      <c r="F36" s="1" t="n">
-        <v>234.0</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I36" s="1" t="n">
+      <c r="F36" s="1">
+        <v>234</v>
+      </c>
+      <c r="G36" s="1">
+        <v>25</v>
+      </c>
+      <c r="H36" s="1">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
         <v>28.57</v>
       </c>
-      <c r="J36" s="1" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="J36" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>26</v>
       </c>
@@ -1268,26 +1631,26 @@
       <c r="D37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="1">
         <v>3926.73</v>
       </c>
-      <c r="F37" s="1" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I37" s="1" t="n">
+      <c r="F37" s="1">
+        <v>86</v>
+      </c>
+      <c r="G37" s="1">
+        <v>11</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+      <c r="I37" s="1">
         <v>33.33</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="1">
         <v>1.42</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>26</v>
       </c>
@@ -1300,26 +1663,26 @@
       <c r="D38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="1">
         <v>3896.05</v>
       </c>
-      <c r="F38" s="1" t="n">
-        <v>285.0</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="H38" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I38" s="1" t="n">
+      <c r="F38" s="1">
+        <v>285</v>
+      </c>
+      <c r="G38" s="1">
+        <v>12</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
         <v>23.08</v>
       </c>
-      <c r="J38" s="1" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="J38" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>28</v>
       </c>
@@ -1332,26 +1695,26 @@
       <c r="D39" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="1">
         <v>3754.99</v>
       </c>
-      <c r="F39" s="1" t="n">
-        <v>21936.0</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>424.0</v>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I39" s="1" t="n">
+      <c r="F39" s="1">
+        <v>21936</v>
+      </c>
+      <c r="G39" s="1">
+        <v>424</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>41.18</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="1">
         <v>1.04</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
@@ -1364,26 +1727,26 @@
       <c r="D40" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="1">
         <v>3686.31</v>
       </c>
-      <c r="F40" s="1" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I40" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="F40" s="1">
+        <v>61</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>23</v>
       </c>
@@ -1396,26 +1759,26 @@
       <c r="D41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="1">
         <v>3312.31</v>
       </c>
-      <c r="F41" s="1" t="n">
-        <v>123.0</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="H41" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I41" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J41" s="1" t="n">
+      <c r="F41" s="1">
+        <v>123</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1">
+        <v>4</v>
+      </c>
+      <c r="I41" s="1">
+        <v>25</v>
+      </c>
+      <c r="J41" s="1">
         <v>1.42</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
@@ -1428,26 +1791,26 @@
       <c r="D42" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="1">
         <v>3293.58</v>
       </c>
-      <c r="F42" s="1" t="n">
-        <v>142.0</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H42" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I42" s="1" t="n">
+      <c r="F42" s="1">
+        <v>142</v>
+      </c>
+      <c r="G42" s="1">
+        <v>8</v>
+      </c>
+      <c r="H42" s="1">
+        <v>4</v>
+      </c>
+      <c r="I42" s="1">
         <v>22.22</v>
       </c>
-      <c r="J42" s="1" t="n">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="J42" s="1">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,26 +1823,26 @@
       <c r="D43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="1">
         <v>3228.36</v>
       </c>
-      <c r="F43" s="1" t="n">
-        <v>6136.0</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>211.0</v>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="I43" s="1" t="n">
+      <c r="F43" s="1">
+        <v>6136</v>
+      </c>
+      <c r="G43" s="1">
+        <v>211</v>
+      </c>
+      <c r="H43" s="1">
+        <v>5</v>
+      </c>
+      <c r="I43" s="1">
         <v>36.9</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="1">
         <v>1.08</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,26 +1855,26 @@
       <c r="D44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="1">
         <v>3176.05</v>
       </c>
-      <c r="F44" s="1" t="n">
-        <v>212.0</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H44" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I44" s="1" t="n">
+      <c r="F44" s="1">
+        <v>212</v>
+      </c>
+      <c r="G44" s="1">
+        <v>15</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
         <v>23.08</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="1">
         <v>1.31</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
@@ -1524,26 +1887,26 @@
       <c r="D45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="1">
         <v>3166.96</v>
       </c>
-      <c r="F45" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H45" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="J45" s="1" t="n">
+      <c r="F45" s="1">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1">
+        <v>3</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="1">
+        <v>50</v>
+      </c>
+      <c r="J45" s="1">
         <v>1.25</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
@@ -1556,26 +1919,26 @@
       <c r="D46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="1">
         <v>3139.66</v>
       </c>
-      <c r="F46" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H46" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="F46" s="1">
+        <v>20</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1">
+        <v>50</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>28</v>
       </c>
@@ -1588,26 +1951,26 @@
       <c r="D47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="1">
         <v>2939.3</v>
       </c>
-      <c r="F47" s="1" t="n">
-        <v>13493.0</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>441.0</v>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I47" s="1" t="n">
+      <c r="F47" s="1">
+        <v>13493</v>
+      </c>
+      <c r="G47" s="1">
+        <v>441</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" s="1">
         <v>35.75</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>28</v>
       </c>
@@ -1620,26 +1983,26 @@
       <c r="D48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="1">
         <v>2830.45</v>
       </c>
-      <c r="F48" s="1" t="n">
-        <v>8196.0</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>174.0</v>
-      </c>
-      <c r="H48" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I48" s="1" t="n">
+      <c r="F48" s="1">
+        <v>8196</v>
+      </c>
+      <c r="G48" s="1">
+        <v>174</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1">
         <v>47.37</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="1">
         <v>1.03</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>30</v>
       </c>
@@ -1652,26 +2015,26 @@
       <c r="D49" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="1">
         <v>2720.5</v>
       </c>
-      <c r="F49" s="1" t="n">
-        <v>109.0</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J49" s="1" t="n">
+      <c r="F49" s="1">
+        <v>109</v>
+      </c>
+      <c r="G49" s="1">
+        <v>9</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
         <v>1.63</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>28</v>
       </c>
@@ -1684,26 +2047,26 @@
       <c r="D50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="1" t="n">
-        <v>2198.7</v>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>14433.0</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>239.0</v>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="I50" s="1" t="n">
+      <c r="E50" s="1">
+        <v>2198.6999999999998</v>
+      </c>
+      <c r="F50" s="1">
+        <v>14433</v>
+      </c>
+      <c r="G50" s="1">
+        <v>239</v>
+      </c>
+      <c r="H50" s="1">
+        <v>7</v>
+      </c>
+      <c r="I50" s="1">
         <v>35.19</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="1">
         <v>1.03</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,26 +2079,26 @@
       <c r="D51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="1">
         <v>2187.73</v>
       </c>
-      <c r="F51" s="1" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I51" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="J51" s="1" t="n">
+      <c r="F51" s="1">
+        <v>63</v>
+      </c>
+      <c r="G51" s="1">
+        <v>4</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>20</v>
+      </c>
+      <c r="J51" s="1">
         <v>1.4</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>30</v>
       </c>
@@ -1748,26 +2111,26 @@
       <c r="D52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="1">
         <v>2038.67</v>
       </c>
-      <c r="F52" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J52" s="1" t="n">
+      <c r="F52" s="1">
+        <v>7</v>
+      </c>
+      <c r="G52" s="1">
+        <v>5</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1">
         <v>1.4</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>30</v>
       </c>
@@ -1780,26 +2143,26 @@
       <c r="D53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="1">
         <v>1879.32</v>
       </c>
-      <c r="F53" s="1" t="n">
-        <v>145.0</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H53" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I53" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="F53" s="1">
+        <v>145</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>34</v>
       </c>
@@ -1812,26 +2175,26 @@
       <c r="D54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="1">
         <v>1853.57</v>
       </c>
-      <c r="F54" s="1" t="n">
-        <v>11386.0</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>149.0</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>37.41</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="F54" s="1">
+        <v>11386</v>
+      </c>
+      <c r="G54" s="1">
+        <v>149</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>37.409999999999997</v>
+      </c>
+      <c r="J54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>15</v>
       </c>
@@ -1844,26 +2207,26 @@
       <c r="D55" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="1">
         <v>1794.53</v>
       </c>
-      <c r="F55" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H55" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="F55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1">
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>34</v>
       </c>
@@ -1876,26 +2239,26 @@
       <c r="D56" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="1">
         <v>1785.97</v>
       </c>
-      <c r="F56" s="1" t="n">
-        <v>14982.0</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>188.0</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I56" s="1" t="n">
+      <c r="F56" s="1">
+        <v>14982</v>
+      </c>
+      <c r="G56" s="1">
+        <v>188</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="1">
         <v>34.32</v>
       </c>
-      <c r="J56" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="J56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -1908,26 +2271,26 @@
       <c r="D57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="1">
         <v>1649.97</v>
       </c>
-      <c r="F57" s="1" t="n">
-        <v>91.0</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H57" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="F57" s="1">
+        <v>91</v>
+      </c>
+      <c r="G57" s="1">
+        <v>5</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="1">
+        <v>40</v>
+      </c>
+      <c r="J57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
@@ -1940,26 +2303,26 @@
       <c r="D58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="1">
         <v>1626.64</v>
       </c>
-      <c r="F58" s="1" t="n">
-        <v>18562.0</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>352.0</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I58" s="1" t="n">
+      <c r="F58" s="1">
+        <v>18562</v>
+      </c>
+      <c r="G58" s="1">
+        <v>352</v>
+      </c>
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" s="1">
         <v>40.14</v>
       </c>
-      <c r="J58" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="J58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>28</v>
       </c>
@@ -1972,26 +2335,26 @@
       <c r="D59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="1">
         <v>1563.42</v>
       </c>
-      <c r="F59" s="1" t="n">
-        <v>8886.0</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>348.0</v>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>40.66</v>
-      </c>
-      <c r="J59" s="1" t="n">
+      <c r="F59" s="1">
+        <v>8886</v>
+      </c>
+      <c r="G59" s="1">
+        <v>348</v>
+      </c>
+      <c r="H59" s="1">
+        <v>2</v>
+      </c>
+      <c r="I59" s="1">
+        <v>40.659999999999997</v>
+      </c>
+      <c r="J59" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>28</v>
       </c>
@@ -2004,26 +2367,26 @@
       <c r="D60" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="1">
         <v>1528.03</v>
       </c>
-      <c r="F60" s="1" t="n">
-        <v>4692.0</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>133.0</v>
-      </c>
-      <c r="H60" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I60" s="1" t="n">
+      <c r="F60" s="1">
+        <v>4692</v>
+      </c>
+      <c r="G60" s="1">
+        <v>133</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="1">
         <v>47.27</v>
       </c>
-      <c r="J60" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="J60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>30</v>
       </c>
@@ -2036,26 +2399,26 @@
       <c r="D61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="1">
         <v>1523.68</v>
       </c>
-      <c r="F61" s="1" t="n">
-        <v>127.0</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="I61" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J61" s="1" t="n">
+      <c r="F61" s="1">
+        <v>127</v>
+      </c>
+      <c r="G61" s="1">
+        <v>4</v>
+      </c>
+      <c r="H61" s="1">
+        <v>4</v>
+      </c>
+      <c r="I61" s="1">
+        <v>25</v>
+      </c>
+      <c r="J61" s="1">
         <v>2.25</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>23</v>
       </c>
@@ -2068,26 +2431,26 @@
       <c r="D62" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="1">
         <v>1366.78</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H62" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J62" s="1" t="n">
+      <c r="F62" s="1">
+        <v>43</v>
+      </c>
+      <c r="G62" s="1">
+        <v>3</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
         <v>1.25</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>36</v>
       </c>
@@ -2100,26 +2463,26 @@
       <c r="D63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="1">
         <v>1348.51</v>
       </c>
-      <c r="F63" s="1" t="n">
-        <v>25504.0</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>148.0</v>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I63" s="1" t="n">
+      <c r="F63" s="1">
+        <v>25504</v>
+      </c>
+      <c r="G63" s="1">
+        <v>148</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1</v>
+      </c>
+      <c r="I63" s="1">
         <v>25.76</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>23</v>
       </c>
@@ -2132,26 +2495,26 @@
       <c r="D64" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E64" s="1" t="n">
-        <v>1184.14</v>
-      </c>
-      <c r="F64" s="1" t="n">
-        <v>239.0</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="H64" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I64" s="1" t="n">
+      <c r="E64" s="1">
+        <v>1184.1400000000001</v>
+      </c>
+      <c r="F64" s="1">
+        <v>239</v>
+      </c>
+      <c r="G64" s="1">
+        <v>10</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="1">
         <v>33.33</v>
       </c>
-      <c r="J64" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="J64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>34</v>
       </c>
@@ -2164,26 +2527,26 @@
       <c r="D65" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="1">
         <v>1147.94</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>11799.0</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>136.0</v>
-      </c>
-      <c r="H65" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I65" s="1" t="n">
+      <c r="F65" s="1">
+        <v>11799</v>
+      </c>
+      <c r="G65" s="1">
+        <v>136</v>
+      </c>
+      <c r="H65" s="1">
+        <v>2</v>
+      </c>
+      <c r="I65" s="1">
         <v>40.43</v>
       </c>
-      <c r="J65" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="J65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
@@ -2196,26 +2559,26 @@
       <c r="D66" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="1">
         <v>1081.52</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>91.0</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="H66" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I66" s="1" t="n">
+      <c r="F66" s="1">
+        <v>91</v>
+      </c>
+      <c r="G66" s="1">
+        <v>6</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
         <v>11.11</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="1">
         <v>1.78</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>28</v>
       </c>
@@ -2228,26 +2591,26 @@
       <c r="D67" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="1">
         <v>1037.33</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>5640.0</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>235.0</v>
-      </c>
-      <c r="H67" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I67" s="1" t="n">
+      <c r="F67" s="1">
+        <v>5640</v>
+      </c>
+      <c r="G67" s="1">
+        <v>235</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3</v>
+      </c>
+      <c r="I67" s="1">
         <v>39.57</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="1">
         <v>1.04</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>28</v>
       </c>
@@ -2260,26 +2623,26 @@
       <c r="D68" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="1">
         <v>1023.16</v>
       </c>
-      <c r="F68" s="1" t="n">
-        <v>6648.0</v>
-      </c>
-      <c r="G68" s="1" t="n">
-        <v>187.0</v>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I68" s="1" t="n">
+      <c r="F68" s="1">
+        <v>6648</v>
+      </c>
+      <c r="G68" s="1">
+        <v>187</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
         <v>38.58</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="1">
         <v>1.05</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>38</v>
       </c>
@@ -2292,26 +2655,26 @@
       <c r="D69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="1">
         <v>997.06</v>
       </c>
-      <c r="F69" s="1" t="n">
-        <v>22186.0</v>
-      </c>
-      <c r="G69" s="1" t="n">
-        <v>203.0</v>
-      </c>
-      <c r="H69" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I69" s="1" t="n">
+      <c r="F69" s="1">
+        <v>22186</v>
+      </c>
+      <c r="G69" s="1">
+        <v>203</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
         <v>26.02</v>
       </c>
-      <c r="J69" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="J69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
@@ -2324,26 +2687,26 @@
       <c r="D70" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="1">
         <v>951.62</v>
       </c>
-      <c r="F70" s="1" t="n">
-        <v>17012.0</v>
-      </c>
-      <c r="G70" s="1" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="H70" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I70" s="1" t="n">
+      <c r="F70" s="1">
+        <v>17012</v>
+      </c>
+      <c r="G70" s="1">
+        <v>69</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1">
         <v>31.67</v>
       </c>
-      <c r="J70" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="J70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
@@ -2356,26 +2719,26 @@
       <c r="D71" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="1">
         <v>948.94</v>
       </c>
-      <c r="F71" s="1" t="n">
-        <v>9432.0</v>
-      </c>
-      <c r="G71" s="1" t="n">
-        <v>192.0</v>
-      </c>
-      <c r="H71" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I71" s="1" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="J71" s="1" t="n">
+      <c r="F71" s="1">
+        <v>9432</v>
+      </c>
+      <c r="G71" s="1">
+        <v>192</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>35</v>
+      </c>
+      <c r="J71" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>34</v>
       </c>
@@ -2388,26 +2751,26 @@
       <c r="D72" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="1">
         <v>874.56</v>
       </c>
-      <c r="F72" s="1" t="n">
-        <v>6776.0</v>
-      </c>
-      <c r="G72" s="1" t="n">
-        <v>115.0</v>
-      </c>
-      <c r="H72" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I72" s="1" t="n">
-        <v>37.84</v>
-      </c>
-      <c r="J72" s="1" t="n">
+      <c r="F72" s="1">
+        <v>6776</v>
+      </c>
+      <c r="G72" s="1">
+        <v>115</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+      <c r="I72" s="1">
+        <v>37.840000000000003</v>
+      </c>
+      <c r="J72" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>30</v>
       </c>
@@ -2420,26 +2783,26 @@
       <c r="D73" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="1">
         <v>827.1</v>
       </c>
-      <c r="F73" s="1" t="n">
-        <v>96.0</v>
-      </c>
-      <c r="G73" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H73" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I73" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="J73" s="1" t="n">
+      <c r="F73" s="1">
+        <v>96</v>
+      </c>
+      <c r="G73" s="1">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+      <c r="I73" s="1">
+        <v>20</v>
+      </c>
+      <c r="J73" s="1">
         <v>1.4</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>36</v>
       </c>
@@ -2452,26 +2815,26 @@
       <c r="D74" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E74" s="1">
         <v>648.78</v>
       </c>
-      <c r="F74" s="1" t="n">
-        <v>5914.0</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>114.0</v>
-      </c>
-      <c r="H74" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I74" s="1" t="n">
+      <c r="F74" s="1">
+        <v>5914</v>
+      </c>
+      <c r="G74" s="1">
+        <v>114</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="1">
         <v>25.77</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="1">
         <v>1.01</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>28</v>
       </c>
@@ -2484,26 +2847,26 @@
       <c r="D75" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E75" s="1" t="n">
+      <c r="E75" s="1">
         <v>643.99</v>
       </c>
-      <c r="F75" s="1" t="n">
-        <v>1562.0</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="H75" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I75" s="1" t="n">
+      <c r="F75" s="1">
+        <v>1562</v>
+      </c>
+      <c r="G75" s="1">
+        <v>83</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+      <c r="I75" s="1">
         <v>24.59</v>
       </c>
-      <c r="J75" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="J75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>40</v>
       </c>
@@ -2516,26 +2879,26 @@
       <c r="D76" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E76" s="1" t="n">
-        <v>620.17</v>
-      </c>
-      <c r="F76" s="1" t="n">
-        <v>21491.0</v>
-      </c>
-      <c r="G76" s="1" t="n">
-        <v>83.0</v>
-      </c>
-      <c r="H76" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I76" s="1" t="n">
+      <c r="E76" s="1">
+        <v>620.16999999999996</v>
+      </c>
+      <c r="F76" s="1">
+        <v>21491</v>
+      </c>
+      <c r="G76" s="1">
+        <v>83</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+      <c r="I76" s="1">
         <v>41.54</v>
       </c>
-      <c r="J76" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="77">
+      <c r="J76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>38</v>
       </c>
@@ -2548,26 +2911,26 @@
       <c r="D77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E77" s="1" t="n">
+      <c r="E77" s="1">
         <v>591.04</v>
       </c>
-      <c r="F77" s="1" t="n">
-        <v>8595.0</v>
-      </c>
-      <c r="G77" s="1" t="n">
-        <v>163.0</v>
-      </c>
-      <c r="H77" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I77" s="1" t="n">
+      <c r="F77" s="1">
+        <v>8595</v>
+      </c>
+      <c r="G77" s="1">
+        <v>163</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
         <v>34.44</v>
       </c>
-      <c r="J77" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="78">
+      <c r="J77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>28</v>
       </c>
@@ -2580,26 +2943,26 @@
       <c r="D78" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E78" s="1" t="n">
-        <v>579.82</v>
-      </c>
-      <c r="F78" s="1" t="n">
-        <v>1906.0</v>
-      </c>
-      <c r="G78" s="1" t="n">
-        <v>74.0</v>
-      </c>
-      <c r="H78" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I78" s="1" t="n">
+      <c r="E78" s="1">
+        <v>579.82000000000005</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1906</v>
+      </c>
+      <c r="G78" s="1">
+        <v>74</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1">
         <v>43.75</v>
       </c>
-      <c r="J78" s="1" t="n">
+      <c r="J78" s="1">
         <v>1.05</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,26 +2975,26 @@
       <c r="D79" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E79" s="1" t="n">
-        <v>570.82</v>
-      </c>
-      <c r="F79" s="1" t="n">
-        <v>162.0</v>
-      </c>
-      <c r="G79" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H79" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I79" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J79" s="1" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="80">
+      <c r="E79" s="1">
+        <v>570.82000000000005</v>
+      </c>
+      <c r="F79" s="1">
+        <v>162</v>
+      </c>
+      <c r="G79" s="1">
+        <v>2</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1</v>
+      </c>
+      <c r="I79" s="1">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
@@ -2644,26 +3007,26 @@
       <c r="D80" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E80" s="1" t="n">
+      <c r="E80" s="1">
         <v>560.73</v>
       </c>
-      <c r="F80" s="1" t="n">
-        <v>5396.0</v>
-      </c>
-      <c r="G80" s="1" t="n">
-        <v>103.0</v>
-      </c>
-      <c r="H80" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I80" s="1" t="n">
+      <c r="F80" s="1">
+        <v>5396</v>
+      </c>
+      <c r="G80" s="1">
+        <v>103</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+      <c r="I80" s="1">
         <v>23.71</v>
       </c>
-      <c r="J80" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="J80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>36</v>
       </c>
@@ -2676,26 +3039,26 @@
       <c r="D81" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E81" s="1" t="n">
+      <c r="E81" s="1">
         <v>555.59</v>
       </c>
-      <c r="F81" s="1" t="n">
-        <v>3606.0</v>
-      </c>
-      <c r="G81" s="1" t="n">
-        <v>78.0</v>
-      </c>
-      <c r="H81" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I81" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J81" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="F81" s="1">
+        <v>3606</v>
+      </c>
+      <c r="G81" s="1">
+        <v>78</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+      <c r="I81" s="1">
+        <v>25</v>
+      </c>
+      <c r="J81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>28</v>
       </c>
@@ -2708,26 +3071,26 @@
       <c r="D82" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E82" s="1" t="n">
+      <c r="E82" s="1">
         <v>541.6</v>
       </c>
-      <c r="F82" s="1" t="n">
-        <v>3220.0</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>142.0</v>
-      </c>
-      <c r="H82" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="I82" s="1" t="n">
+      <c r="F82" s="1">
+        <v>3220</v>
+      </c>
+      <c r="G82" s="1">
+        <v>142</v>
+      </c>
+      <c r="H82" s="1">
+        <v>3</v>
+      </c>
+      <c r="I82" s="1">
         <v>49.07</v>
       </c>
-      <c r="J82" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="83">
+      <c r="J82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>40</v>
       </c>
@@ -2740,26 +3103,26 @@
       <c r="D83" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="E83" s="1">
         <v>517.62</v>
       </c>
-      <c r="F83" s="1" t="n">
-        <v>17338.0</v>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>51.0</v>
-      </c>
-      <c r="H83" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I83" s="1" t="n">
+      <c r="F83" s="1">
+        <v>17338</v>
+      </c>
+      <c r="G83" s="1">
+        <v>51</v>
+      </c>
+      <c r="H83" s="1">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1">
         <v>60.61</v>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="J83" s="1">
         <v>1.03</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>36</v>
       </c>
@@ -2772,26 +3135,26 @@
       <c r="D84" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E84" s="1" t="n">
-        <v>516.05</v>
-      </c>
-      <c r="F84" s="1" t="n">
-        <v>6389.0</v>
-      </c>
-      <c r="G84" s="1" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="H84" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I84" s="1" t="n">
+      <c r="E84" s="1">
+        <v>516.04999999999995</v>
+      </c>
+      <c r="F84" s="1">
+        <v>6389</v>
+      </c>
+      <c r="G84" s="1">
+        <v>100</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+      <c r="I84" s="1">
         <v>36.78</v>
       </c>
-      <c r="J84" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="J84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>38</v>
       </c>
@@ -2804,26 +3167,26 @@
       <c r="D85" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E85" s="1" t="n">
-        <v>514.81</v>
-      </c>
-      <c r="F85" s="1" t="n">
-        <v>7439.0</v>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>140.0</v>
-      </c>
-      <c r="H85" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I85" s="1" t="n">
+      <c r="E85" s="1">
+        <v>514.80999999999995</v>
+      </c>
+      <c r="F85" s="1">
+        <v>7439</v>
+      </c>
+      <c r="G85" s="1">
+        <v>140</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+      <c r="I85" s="1">
         <v>37.69</v>
       </c>
-      <c r="J85" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="86">
+      <c r="J85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>38</v>
       </c>
@@ -2836,26 +3199,26 @@
       <c r="D86" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E86" s="1" t="n">
+      <c r="E86" s="1">
         <v>506.68</v>
       </c>
-      <c r="F86" s="1" t="n">
-        <v>5378.0</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>138.0</v>
-      </c>
-      <c r="H86" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I86" s="1" t="n">
+      <c r="F86" s="1">
+        <v>5378</v>
+      </c>
+      <c r="G86" s="1">
+        <v>138</v>
+      </c>
+      <c r="H86" s="1">
+        <v>0</v>
+      </c>
+      <c r="I86" s="1">
         <v>28.07</v>
       </c>
-      <c r="J86" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="J86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>36</v>
       </c>
@@ -2868,26 +3231,26 @@
       <c r="D87" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E87" s="1" t="n">
+      <c r="E87" s="1">
         <v>492.42</v>
       </c>
-      <c r="F87" s="1" t="n">
-        <v>3524.0</v>
-      </c>
-      <c r="G87" s="1" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="H87" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I87" s="1" t="n">
+      <c r="F87" s="1">
+        <v>3524</v>
+      </c>
+      <c r="G87" s="1">
+        <v>86</v>
+      </c>
+      <c r="H87" s="1">
+        <v>0</v>
+      </c>
+      <c r="I87" s="1">
         <v>20.55</v>
       </c>
-      <c r="J87" s="1" t="n">
+      <c r="J87" s="1">
         <v>1.03</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>30</v>
       </c>
@@ -2900,26 +3263,26 @@
       <c r="D88" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E88" s="1">
         <v>444.47</v>
       </c>
-      <c r="F88" s="1" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="G88" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H88" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I88" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J88" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="F88" s="1">
+        <v>14</v>
+      </c>
+      <c r="G88" s="1">
+        <v>1</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>34</v>
       </c>
@@ -2932,26 +3295,26 @@
       <c r="D89" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E89" s="1" t="n">
+      <c r="E89" s="1">
         <v>439.11</v>
       </c>
-      <c r="F89" s="1" t="n">
-        <v>4418.0</v>
-      </c>
-      <c r="G89" s="1" t="n">
-        <v>148.0</v>
-      </c>
-      <c r="H89" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I89" s="1" t="n">
+      <c r="F89" s="1">
+        <v>4418</v>
+      </c>
+      <c r="G89" s="1">
+        <v>148</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1">
         <v>46.46</v>
       </c>
-      <c r="J89" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="J89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>36</v>
       </c>
@@ -2964,26 +3327,26 @@
       <c r="D90" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E90" s="1" t="n">
+      <c r="E90" s="1">
         <v>401.26</v>
       </c>
-      <c r="F90" s="1" t="n">
-        <v>3318.0</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="H90" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I90" s="1" t="n">
+      <c r="F90" s="1">
+        <v>3318</v>
+      </c>
+      <c r="G90" s="1">
+        <v>61</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1">
         <v>17.39</v>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="J90" s="1">
         <v>1.02</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>23</v>
       </c>
@@ -2996,26 +3359,26 @@
       <c r="D91" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E91" s="1" t="n">
-        <v>394.0</v>
-      </c>
-      <c r="F91" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I91" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J91" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="E91" s="1">
+        <v>394</v>
+      </c>
+      <c r="F91" s="1">
+        <v>10</v>
+      </c>
+      <c r="G91" s="1">
+        <v>1</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>38</v>
       </c>
@@ -3028,26 +3391,26 @@
       <c r="D92" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E92" s="1" t="n">
+      <c r="E92" s="1">
         <v>392.06</v>
       </c>
-      <c r="F92" s="1" t="n">
-        <v>6846.0</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>86.0</v>
-      </c>
-      <c r="H92" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I92" s="1" t="n">
+      <c r="F92" s="1">
+        <v>6846</v>
+      </c>
+      <c r="G92" s="1">
+        <v>86</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
         <v>30.77</v>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="J92" s="1">
         <v>1.03</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>38</v>
       </c>
@@ -3060,26 +3423,26 @@
       <c r="D93" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E93" s="1" t="n">
+      <c r="E93" s="1">
         <v>370.56</v>
       </c>
-      <c r="F93" s="1" t="n">
-        <v>4468.0</v>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>94.0</v>
-      </c>
-      <c r="H93" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I93" s="1" t="n">
+      <c r="F93" s="1">
+        <v>4468</v>
+      </c>
+      <c r="G93" s="1">
+        <v>94</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1">
         <v>30.38</v>
       </c>
-      <c r="J93" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="94">
+      <c r="J93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>23</v>
       </c>
@@ -3092,17 +3455,17 @@
       <c r="D94" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E94" s="1" t="n">
+      <c r="E94" s="1">
         <v>365.27</v>
       </c>
-      <c r="F94" s="1" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H94" s="1" t="n">
-        <v>0.0</v>
+      <c r="F94" s="1">
+        <v>31</v>
+      </c>
+      <c r="G94" s="1">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>42</v>
@@ -3111,7 +3474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>34</v>
       </c>
@@ -3124,26 +3487,26 @@
       <c r="D95" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E95" s="1" t="n">
+      <c r="E95" s="1">
         <v>342.15</v>
       </c>
-      <c r="F95" s="1" t="n">
-        <v>2705.0</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>57.0</v>
-      </c>
-      <c r="H95" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I95" s="1" t="n">
-        <v>34.09</v>
-      </c>
-      <c r="J95" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="F95" s="1">
+        <v>2705</v>
+      </c>
+      <c r="G95" s="1">
+        <v>57</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>34.090000000000003</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>38</v>
       </c>
@@ -3156,26 +3519,26 @@
       <c r="D96" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E96" s="1" t="n">
+      <c r="E96" s="1">
         <v>333.7</v>
       </c>
-      <c r="F96" s="1" t="n">
-        <v>4703.0</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>69.0</v>
-      </c>
-      <c r="H96" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I96" s="1" t="n">
+      <c r="F96" s="1">
+        <v>4703</v>
+      </c>
+      <c r="G96" s="1">
+        <v>69</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
         <v>28.26</v>
       </c>
-      <c r="J96" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="97">
+      <c r="J96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>34</v>
       </c>
@@ -3188,26 +3551,26 @@
       <c r="D97" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E97" s="1" t="n">
-        <v>315.47</v>
-      </c>
-      <c r="F97" s="1" t="n">
-        <v>1897.0</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>53.0</v>
-      </c>
-      <c r="H97" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I97" s="1" t="n">
+      <c r="E97" s="1">
+        <v>315.47000000000003</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1897</v>
+      </c>
+      <c r="G97" s="1">
+        <v>53</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1">
         <v>28.89</v>
       </c>
-      <c r="J97" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="98">
+      <c r="J97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>36</v>
       </c>
@@ -3220,26 +3583,26 @@
       <c r="D98" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E98" s="1" t="n">
+      <c r="E98" s="1">
         <v>311.24</v>
       </c>
-      <c r="F98" s="1" t="n">
-        <v>2313.0</v>
-      </c>
-      <c r="G98" s="1" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="H98" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I98" s="1" t="n">
+      <c r="F98" s="1">
+        <v>2313</v>
+      </c>
+      <c r="G98" s="1">
+        <v>34</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
         <v>32.14</v>
       </c>
-      <c r="J98" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="J98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>36</v>
       </c>
@@ -3252,26 +3615,26 @@
       <c r="D99" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E99" s="1" t="n">
-        <v>297.96</v>
-      </c>
-      <c r="F99" s="1" t="n">
-        <v>4651.0</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>42.0</v>
-      </c>
-      <c r="H99" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I99" s="1" t="n">
+      <c r="E99" s="1">
+        <v>297.95999999999998</v>
+      </c>
+      <c r="F99" s="1">
+        <v>4651</v>
+      </c>
+      <c r="G99" s="1">
+        <v>42</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
         <v>12.12</v>
       </c>
-      <c r="J99" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>23</v>
       </c>
@@ -3284,26 +3647,26 @@
       <c r="D100" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E100" s="1" t="n">
+      <c r="E100" s="1">
         <v>285.36</v>
       </c>
-      <c r="F100" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G100" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H100" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I100" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J100" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="F100" s="1">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>36</v>
       </c>
@@ -3316,26 +3679,26 @@
       <c r="D101" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E101" s="1" t="n">
+      <c r="E101" s="1">
         <v>269.99</v>
       </c>
-      <c r="F101" s="1" t="n">
-        <v>1753.0</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="H101" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I101" s="1" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="J101" s="1" t="n">
+      <c r="F101" s="1">
+        <v>1753</v>
+      </c>
+      <c r="G101" s="1">
+        <v>40</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>16</v>
+      </c>
+      <c r="J101" s="1">
         <v>1.08</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>38</v>
       </c>
@@ -3348,26 +3711,26 @@
       <c r="D102" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E102" s="1" t="n">
+      <c r="E102" s="1">
         <v>232.58</v>
       </c>
-      <c r="F102" s="1" t="n">
-        <v>2949.0</v>
-      </c>
-      <c r="G102" s="1" t="n">
-        <v>52.0</v>
-      </c>
-      <c r="H102" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I102" s="1" t="n">
+      <c r="F102" s="1">
+        <v>2949</v>
+      </c>
+      <c r="G102" s="1">
+        <v>52</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
         <v>30.23</v>
       </c>
-      <c r="J102" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="103">
+      <c r="J102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>28</v>
       </c>
@@ -3380,26 +3743,26 @@
       <c r="D103" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E103" s="1" t="n">
+      <c r="E103" s="1">
         <v>225.13</v>
       </c>
-      <c r="F103" s="1" t="n">
-        <v>1099.0</v>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="H103" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I103" s="1" t="n">
+      <c r="F103" s="1">
+        <v>1099</v>
+      </c>
+      <c r="G103" s="1">
+        <v>35</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
         <v>44.44</v>
       </c>
-      <c r="J103" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="104">
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>38</v>
       </c>
@@ -3412,26 +3775,26 @@
       <c r="D104" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E104" s="1" t="n">
+      <c r="E104" s="1">
         <v>175.6</v>
       </c>
-      <c r="F104" s="1" t="n">
-        <v>2889.0</v>
-      </c>
-      <c r="G104" s="1" t="n">
-        <v>41.0</v>
-      </c>
-      <c r="H104" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I104" s="1" t="n">
+      <c r="F104" s="1">
+        <v>2889</v>
+      </c>
+      <c r="G104" s="1">
+        <v>41</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1">
         <v>38.24</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="1">
         <v>1.06</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>28</v>
       </c>
@@ -3444,26 +3807,26 @@
       <c r="D105" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E105" s="1" t="n">
+      <c r="E105" s="1">
         <v>157.49</v>
       </c>
-      <c r="F105" s="1" t="n">
-        <v>882.0</v>
-      </c>
-      <c r="G105" s="1" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="H105" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I105" s="1" t="n">
+      <c r="F105" s="1">
+        <v>882</v>
+      </c>
+      <c r="G105" s="1">
+        <v>24</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
         <v>31.25</v>
       </c>
-      <c r="J105" s="1" t="n">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="106">
+      <c r="J105" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>38</v>
       </c>
@@ -3476,26 +3839,26 @@
       <c r="D106" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E106" s="1" t="n">
-        <v>155.27</v>
-      </c>
-      <c r="F106" s="1" t="n">
-        <v>3122.0</v>
-      </c>
-      <c r="G106" s="1" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="H106" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I106" s="1" t="n">
+      <c r="E106" s="1">
+        <v>155.27000000000001</v>
+      </c>
+      <c r="F106" s="1">
+        <v>3122</v>
+      </c>
+      <c r="G106" s="1">
+        <v>40</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
         <v>30.23</v>
       </c>
-      <c r="J106" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="107">
+      <c r="J106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>34</v>
       </c>
@@ -3508,26 +3871,26 @@
       <c r="D107" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E107" s="1" t="n">
-        <v>147.17</v>
-      </c>
-      <c r="F107" s="1" t="n">
-        <v>627.0</v>
-      </c>
-      <c r="G107" s="1" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H107" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I107" s="1" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="J107" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="108">
+      <c r="E107" s="1">
+        <v>147.16999999999999</v>
+      </c>
+      <c r="F107" s="1">
+        <v>627</v>
+      </c>
+      <c r="G107" s="1">
+        <v>9</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>30</v>
+      </c>
+      <c r="J107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>34</v>
       </c>
@@ -3540,26 +3903,26 @@
       <c r="D108" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E108" s="1" t="n">
+      <c r="E108" s="1">
         <v>127.41</v>
       </c>
-      <c r="F108" s="1" t="n">
-        <v>994.0</v>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="H108" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I108" s="1" t="n">
+      <c r="F108" s="1">
+        <v>994</v>
+      </c>
+      <c r="G108" s="1">
+        <v>33</v>
+      </c>
+      <c r="H108" s="1">
+        <v>0</v>
+      </c>
+      <c r="I108" s="1">
         <v>32.14</v>
       </c>
-      <c r="J108" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="109">
+      <c r="J108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>38</v>
       </c>
@@ -3572,26 +3935,26 @@
       <c r="D109" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E109" s="1" t="n">
+      <c r="E109" s="1">
         <v>127.36</v>
       </c>
-      <c r="F109" s="1" t="n">
-        <v>1957.0</v>
-      </c>
-      <c r="G109" s="1" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="H109" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I109" s="1" t="n">
+      <c r="F109" s="1">
+        <v>1957</v>
+      </c>
+      <c r="G109" s="1">
+        <v>32</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+      <c r="I109" s="1">
         <v>29.63</v>
       </c>
-      <c r="J109" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="110">
+      <c r="J109" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>30</v>
       </c>
@@ -3604,17 +3967,17 @@
       <c r="D110" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E110" s="1" t="n">
+      <c r="E110" s="1">
         <v>118.63</v>
       </c>
-      <c r="F110" s="1" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G110" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H110" s="1" t="n">
-        <v>0.0</v>
+      <c r="F110" s="1">
+        <v>15</v>
+      </c>
+      <c r="G110" s="1">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>42</v>
@@ -3623,7 +3986,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>36</v>
       </c>
@@ -3636,26 +3999,26 @@
       <c r="D111" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E111" s="1" t="n">
+      <c r="E111" s="1">
         <v>113.75</v>
       </c>
-      <c r="F111" s="1" t="n">
-        <v>781.0</v>
-      </c>
-      <c r="G111" s="1" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="H111" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I111" s="1" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="J111" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="112">
+      <c r="F111" s="1">
+        <v>781</v>
+      </c>
+      <c r="G111" s="1">
+        <v>20</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+      <c r="I111" s="1">
+        <v>28</v>
+      </c>
+      <c r="J111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>38</v>
       </c>
@@ -3668,26 +4031,26 @@
       <c r="D112" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E112" s="1" t="n">
+      <c r="E112" s="1">
         <v>104.16</v>
       </c>
-      <c r="F112" s="1" t="n">
-        <v>2442.0</v>
-      </c>
-      <c r="G112" s="1" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="H112" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I112" s="1" t="n">
+      <c r="F112" s="1">
+        <v>2442</v>
+      </c>
+      <c r="G112" s="1">
+        <v>29</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
         <v>34.78</v>
       </c>
-      <c r="J112" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="113">
+      <c r="J112" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>38</v>
       </c>
@@ -3700,26 +4063,26 @@
       <c r="D113" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E113" s="1" t="n">
+      <c r="E113" s="1">
         <v>97.13</v>
       </c>
-      <c r="F113" s="1" t="n">
-        <v>1061.0</v>
-      </c>
-      <c r="G113" s="1" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="H113" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I113" s="1" t="n">
+      <c r="F113" s="1">
+        <v>1061</v>
+      </c>
+      <c r="G113" s="1">
+        <v>28</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+      <c r="I113" s="1">
         <v>18.18</v>
       </c>
-      <c r="J113" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="114">
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>34</v>
       </c>
@@ -3732,26 +4095,26 @@
       <c r="D114" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E114" s="1" t="n">
+      <c r="E114" s="1">
         <v>94.77</v>
       </c>
-      <c r="F114" s="1" t="n">
-        <v>889.0</v>
-      </c>
-      <c r="G114" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="H114" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I114" s="1" t="n">
+      <c r="F114" s="1">
+        <v>889</v>
+      </c>
+      <c r="G114" s="1">
+        <v>10</v>
+      </c>
+      <c r="H114" s="1">
+        <v>0</v>
+      </c>
+      <c r="I114" s="1">
         <v>33.33</v>
       </c>
-      <c r="J114" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="115">
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>38</v>
       </c>
@@ -3764,26 +4127,26 @@
       <c r="D115" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E115" s="1" t="n">
+      <c r="E115" s="1">
         <v>91.97</v>
       </c>
-      <c r="F115" s="1" t="n">
-        <v>1822.0</v>
-      </c>
-      <c r="G115" s="1" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="H115" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I115" s="1" t="n">
+      <c r="F115" s="1">
+        <v>1822</v>
+      </c>
+      <c r="G115" s="1">
+        <v>19</v>
+      </c>
+      <c r="H115" s="1">
+        <v>0</v>
+      </c>
+      <c r="I115" s="1">
         <v>47.37</v>
       </c>
-      <c r="J115" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="116">
+      <c r="J115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>38</v>
       </c>
@@ -3796,26 +4159,26 @@
       <c r="D116" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E116" s="1" t="n">
+      <c r="E116" s="1">
         <v>87.29</v>
       </c>
-      <c r="F116" s="1" t="n">
-        <v>1336.0</v>
-      </c>
-      <c r="G116" s="1" t="n">
-        <v>23.0</v>
-      </c>
-      <c r="H116" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I116" s="1" t="n">
+      <c r="F116" s="1">
+        <v>1336</v>
+      </c>
+      <c r="G116" s="1">
+        <v>23</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+      <c r="I116" s="1">
         <v>5.88</v>
       </c>
-      <c r="J116" s="1" t="n">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="117">
+      <c r="J116" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>36</v>
       </c>
@@ -3828,26 +4191,26 @@
       <c r="D117" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E117" s="1" t="n">
+      <c r="E117" s="1">
         <v>86.53</v>
       </c>
-      <c r="F117" s="1" t="n">
-        <v>365.0</v>
-      </c>
-      <c r="G117" s="1" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="H117" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I117" s="1" t="n">
+      <c r="F117" s="1">
+        <v>365</v>
+      </c>
+      <c r="G117" s="1">
+        <v>14</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
         <v>35.71</v>
       </c>
-      <c r="J117" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="118">
+      <c r="J117" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>36</v>
       </c>
@@ -3860,26 +4223,26 @@
       <c r="D118" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E118" s="1" t="n">
+      <c r="E118" s="1">
         <v>79.2</v>
       </c>
-      <c r="F118" s="1" t="n">
-        <v>1159.0</v>
-      </c>
-      <c r="G118" s="1" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="H118" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I118" s="1" t="n">
+      <c r="F118" s="1">
+        <v>1159</v>
+      </c>
+      <c r="G118" s="1">
+        <v>15</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
         <v>11.11</v>
       </c>
-      <c r="J118" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="119">
+      <c r="J118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>40</v>
       </c>
@@ -3892,26 +4255,26 @@
       <c r="D119" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E119" s="1" t="n">
+      <c r="E119" s="1">
         <v>76.75</v>
       </c>
-      <c r="F119" s="1" t="n">
-        <v>2253.0</v>
-      </c>
-      <c r="G119" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H119" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I119" s="1" t="n">
+      <c r="F119" s="1">
+        <v>2253</v>
+      </c>
+      <c r="G119" s="1">
+        <v>7</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
         <v>37.5</v>
       </c>
-      <c r="J119" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="120">
+      <c r="J119" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>34</v>
       </c>
@@ -3924,26 +4287,26 @@
       <c r="D120" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E120" s="1" t="n">
-        <v>75.29</v>
-      </c>
-      <c r="F120" s="1" t="n">
-        <v>756.0</v>
-      </c>
-      <c r="G120" s="1" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="H120" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I120" s="1" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="J120" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="121">
+      <c r="E120" s="1">
+        <v>75.290000000000006</v>
+      </c>
+      <c r="F120" s="1">
+        <v>756</v>
+      </c>
+      <c r="G120" s="1">
+        <v>12</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+      <c r="I120" s="1">
+        <v>40</v>
+      </c>
+      <c r="J120" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>40</v>
       </c>
@@ -3956,26 +4319,26 @@
       <c r="D121" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E121" s="1" t="n">
+      <c r="E121" s="1">
         <v>69.34</v>
       </c>
-      <c r="F121" s="1" t="n">
-        <v>1255.0</v>
-      </c>
-      <c r="G121" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H121" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I121" s="1" t="n">
+      <c r="F121" s="1">
+        <v>1255</v>
+      </c>
+      <c r="G121" s="1">
+        <v>7</v>
+      </c>
+      <c r="H121" s="1">
+        <v>0</v>
+      </c>
+      <c r="I121" s="1">
         <v>33.33</v>
       </c>
-      <c r="J121" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="122">
+      <c r="J121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>38</v>
       </c>
@@ -3988,26 +4351,26 @@
       <c r="D122" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E122" s="1" t="n">
-        <v>65.76</v>
-      </c>
-      <c r="F122" s="1" t="n">
-        <v>675.0</v>
-      </c>
-      <c r="G122" s="1" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="H122" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I122" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="J122" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="123">
+      <c r="E122" s="1">
+        <v>65.760000000000005</v>
+      </c>
+      <c r="F122" s="1">
+        <v>675</v>
+      </c>
+      <c r="G122" s="1">
+        <v>17</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+      <c r="I122" s="1">
+        <v>10</v>
+      </c>
+      <c r="J122" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>40</v>
       </c>
@@ -4020,26 +4383,26 @@
       <c r="D123" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E123" s="1" t="n">
+      <c r="E123" s="1">
         <v>56.29</v>
       </c>
-      <c r="F123" s="1" t="n">
-        <v>587.0</v>
-      </c>
-      <c r="G123" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H123" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I123" s="1" t="n">
+      <c r="F123" s="1">
+        <v>587</v>
+      </c>
+      <c r="G123" s="1">
+        <v>7</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+      <c r="I123" s="1">
         <v>28.57</v>
       </c>
-      <c r="J123" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="124">
+      <c r="J123" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>34</v>
       </c>
@@ -4052,26 +4415,26 @@
       <c r="D124" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E124" s="1" t="n">
+      <c r="E124" s="1">
         <v>49.1</v>
       </c>
-      <c r="F124" s="1" t="n">
-        <v>323.0</v>
-      </c>
-      <c r="G124" s="1" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="H124" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I124" s="1" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="J124" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="125">
+      <c r="F124" s="1">
+        <v>323</v>
+      </c>
+      <c r="G124" s="1">
+        <v>13</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>25</v>
+      </c>
+      <c r="J124" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>38</v>
       </c>
@@ -4084,26 +4447,26 @@
       <c r="D125" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E125" s="1" t="n">
+      <c r="E125" s="1">
         <v>48.79</v>
       </c>
-      <c r="F125" s="1" t="n">
-        <v>890.0</v>
-      </c>
-      <c r="G125" s="1" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="H125" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I125" s="1" t="n">
+      <c r="F125" s="1">
+        <v>890</v>
+      </c>
+      <c r="G125" s="1">
+        <v>13</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+      <c r="I125" s="1">
         <v>33.33</v>
       </c>
-      <c r="J125" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="126">
+      <c r="J125" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>40</v>
       </c>
@@ -4116,26 +4479,26 @@
       <c r="D126" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E126" s="1" t="n">
+      <c r="E126" s="1">
         <v>43.66</v>
       </c>
-      <c r="F126" s="1" t="n">
-        <v>347.0</v>
-      </c>
-      <c r="G126" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H126" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I126" s="1" t="n">
+      <c r="F126" s="1">
+        <v>347</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1">
         <v>33.33</v>
       </c>
-      <c r="J126" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="127">
+      <c r="J126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>40</v>
       </c>
@@ -4148,26 +4511,26 @@
       <c r="D127" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E127" s="1" t="n">
+      <c r="E127" s="1">
         <v>36.64</v>
       </c>
-      <c r="F127" s="1" t="n">
-        <v>1318.0</v>
-      </c>
-      <c r="G127" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H127" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I127" s="1" t="n">
+      <c r="F127" s="1">
+        <v>1318</v>
+      </c>
+      <c r="G127" s="1">
+        <v>8</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+      <c r="I127" s="1">
         <v>33.33</v>
       </c>
-      <c r="J127" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="128">
+      <c r="J127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>36</v>
       </c>
@@ -4180,26 +4543,26 @@
       <c r="D128" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E128" s="1" t="n">
+      <c r="E128" s="1">
         <v>34.89</v>
       </c>
-      <c r="F128" s="1" t="n">
-        <v>572.0</v>
-      </c>
-      <c r="G128" s="1" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="H128" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I128" s="1" t="n">
+      <c r="F128" s="1">
+        <v>572</v>
+      </c>
+      <c r="G128" s="1">
+        <v>8</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+      <c r="I128" s="1">
         <v>14.29</v>
       </c>
-      <c r="J128" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="129">
+      <c r="J128" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>40</v>
       </c>
@@ -4212,26 +4575,26 @@
       <c r="D129" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E129" s="1" t="n">
-        <v>33.84</v>
-      </c>
-      <c r="F129" s="1" t="n">
-        <v>767.0</v>
-      </c>
-      <c r="G129" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="H129" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I129" s="1" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J129" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="130">
+      <c r="E129" s="1">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="F129" s="1">
+        <v>767</v>
+      </c>
+      <c r="G129" s="1">
+        <v>6</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+      <c r="I129" s="1">
+        <v>100</v>
+      </c>
+      <c r="J129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,26 +4607,26 @@
       <c r="D130" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E130" s="1" t="n">
+      <c r="E130" s="1">
         <v>30.81</v>
       </c>
-      <c r="F130" s="1" t="n">
-        <v>1266.0</v>
-      </c>
-      <c r="G130" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="H130" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I130" s="1" t="n">
+      <c r="F130" s="1">
+        <v>1266</v>
+      </c>
+      <c r="G130" s="1">
+        <v>6</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+      <c r="I130" s="1">
         <v>66.67</v>
       </c>
-      <c r="J130" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="131">
+      <c r="J130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>40</v>
       </c>
@@ -4276,26 +4639,26 @@
       <c r="D131" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E131" s="1" t="n">
+      <c r="E131" s="1">
         <v>28.27</v>
       </c>
-      <c r="F131" s="1" t="n">
-        <v>427.0</v>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H131" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I131" s="1" t="n">
+      <c r="F131" s="1">
+        <v>427</v>
+      </c>
+      <c r="G131" s="1">
+        <v>3</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
         <v>33.33</v>
       </c>
-      <c r="J131" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="132">
+      <c r="J131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>40</v>
       </c>
@@ -4308,26 +4671,26 @@
       <c r="D132" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E132" s="1" t="n">
+      <c r="E132" s="1">
         <v>23.94</v>
       </c>
-      <c r="F132" s="1" t="n">
-        <v>958.0</v>
-      </c>
-      <c r="G132" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H132" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I132" s="1" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="J132" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="133">
+      <c r="F132" s="1">
+        <v>958</v>
+      </c>
+      <c r="G132" s="1">
+        <v>4</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+      <c r="I132" s="1">
+        <v>50</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>40</v>
       </c>
@@ -4340,26 +4703,26 @@
       <c r="D133" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E133" s="1" t="n">
+      <c r="E133" s="1">
         <v>23.3</v>
       </c>
-      <c r="F133" s="1" t="n">
-        <v>592.0</v>
-      </c>
-      <c r="G133" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H133" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I133" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J133" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="134">
+      <c r="F133" s="1">
+        <v>592</v>
+      </c>
+      <c r="G133" s="1">
+        <v>3</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+      <c r="I133" s="1">
+        <v>0</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>40</v>
       </c>
@@ -4372,26 +4735,26 @@
       <c r="D134" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E134" s="1" t="n">
+      <c r="E134" s="1">
         <v>20.29</v>
       </c>
-      <c r="F134" s="1" t="n">
-        <v>838.0</v>
-      </c>
-      <c r="G134" s="1" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="H134" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I134" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="J134" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="135">
+      <c r="F134" s="1">
+        <v>838</v>
+      </c>
+      <c r="G134" s="1">
+        <v>4</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+      <c r="I134" s="1">
+        <v>0</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>38</v>
       </c>
@@ -4404,26 +4767,26 @@
       <c r="D135" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E135" s="1" t="n">
-        <v>9.13</v>
-      </c>
-      <c r="F135" s="1" t="n">
-        <v>232.0</v>
-      </c>
-      <c r="G135" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H135" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I135" s="1" t="n">
-        <v>75.0</v>
-      </c>
-      <c r="J135" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="136">
+      <c r="E135" s="1">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="F135" s="1">
+        <v>232</v>
+      </c>
+      <c r="G135" s="1">
+        <v>5</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+      <c r="I135" s="1">
+        <v>75</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>40</v>
       </c>
@@ -4436,17 +4799,17 @@
       <c r="D136" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E136" s="1" t="n">
+      <c r="E136" s="1">
         <v>6.59</v>
       </c>
-      <c r="F136" s="1" t="n">
-        <v>287.0</v>
-      </c>
-      <c r="G136" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H136" s="1" t="n">
-        <v>0.0</v>
+      <c r="F136" s="1">
+        <v>287</v>
+      </c>
+      <c r="G136" s="1">
+        <v>1</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>42</v>
@@ -4455,7 +4818,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>34</v>
       </c>
@@ -4468,26 +4831,26 @@
       <c r="D137" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E137" s="1" t="n">
+      <c r="E137" s="1">
         <v>4.63</v>
       </c>
-      <c r="F137" s="1" t="n">
-        <v>274.0</v>
-      </c>
-      <c r="G137" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H137" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I137" s="1" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="J137" s="1" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="138">
+      <c r="F137" s="1">
+        <v>274</v>
+      </c>
+      <c r="G137" s="1">
+        <v>3</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>50</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>30</v>
       </c>
@@ -4500,17 +4863,17 @@
       <c r="D138" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E138" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F138" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G138" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H138" s="1" t="n">
-        <v>0.0</v>
+      <c r="E138" s="1">
+        <v>0</v>
+      </c>
+      <c r="F138" s="1">
+        <v>10</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>42</v>
@@ -4519,7 +4882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>40</v>
       </c>
@@ -4532,17 +4895,17 @@
       <c r="D139" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E139" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F139" s="1" t="n">
-        <v>34.0</v>
-      </c>
-      <c r="G139" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H139" s="1" t="n">
-        <v>0.0</v>
+      <c r="E139" s="1">
+        <v>0</v>
+      </c>
+      <c r="F139" s="1">
+        <v>34</v>
+      </c>
+      <c r="G139" s="1">
+        <v>0</v>
+      </c>
+      <c r="H139" s="1">
+        <v>0</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>42</v>
@@ -4551,7 +4914,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>26</v>
       </c>
@@ -4564,17 +4927,17 @@
       <c r="D140" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E140" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F140" s="1" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="G140" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H140" s="1" t="n">
-        <v>0.0</v>
+      <c r="E140" s="1">
+        <v>0</v>
+      </c>
+      <c r="F140" s="1">
+        <v>24</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>42</v>
@@ -4583,7 +4946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>26</v>
       </c>
@@ -4596,17 +4959,17 @@
       <c r="D141" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E141" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F141" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G141" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H141" s="1" t="n">
-        <v>0.0</v>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="1">
+        <v>10</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>42</v>
@@ -4615,7 +4978,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>23</v>
       </c>
@@ -4628,17 +4991,17 @@
       <c r="D142" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E142" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F142" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G142" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H142" s="1" t="n">
-        <v>0.0</v>
+      <c r="E142" s="1">
+        <v>0</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>42</v>
@@ -4647,7 +5010,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>26</v>
       </c>
@@ -4660,17 +5023,17 @@
       <c r="D143" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E143" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F143" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G143" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H143" s="1" t="n">
-        <v>0.0</v>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+      <c r="F143" s="1">
+        <v>3</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>42</v>
@@ -4679,7 +5042,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>15</v>
       </c>
@@ -4692,17 +5055,17 @@
       <c r="D144" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E144" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F144" s="1" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="G144" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H144" s="1" t="n">
-        <v>0.0</v>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="1">
+        <v>17</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>42</v>
@@ -4711,7 +5074,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>15</v>
       </c>
@@ -4724,17 +5087,17 @@
       <c r="D145" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E145" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F145" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G145" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H145" s="1" t="n">
-        <v>0.0</v>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="1">
+        <v>3</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>42</v>
@@ -4743,7 +5106,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>40</v>
       </c>
@@ -4756,17 +5119,17 @@
       <c r="D146" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E146" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F146" s="1" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="G146" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H146" s="1" t="n">
-        <v>0.0</v>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1">
+        <v>79</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>42</v>
@@ -4775,7 +5138,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>40</v>
       </c>
@@ -4788,17 +5151,17 @@
       <c r="D147" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E147" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F147" s="1" t="n">
-        <v>63.0</v>
-      </c>
-      <c r="G147" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H147" s="1" t="n">
-        <v>0.0</v>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1">
+        <v>63</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>42</v>
@@ -4807,7 +5170,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>23</v>
       </c>
@@ -4820,17 +5183,17 @@
       <c r="D148" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E148" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F148" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G148" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H148" s="1" t="n">
-        <v>0.0</v>
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1">
+        <v>5</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>42</v>
@@ -4839,7 +5202,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>30</v>
       </c>
@@ -4852,17 +5215,17 @@
       <c r="D149" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E149" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F149" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G149" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H149" s="1" t="n">
-        <v>0.0</v>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>42</v>
@@ -4871,7 +5234,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>30</v>
       </c>
@@ -4884,17 +5247,17 @@
       <c r="D150" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E150" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F150" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G150" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H150" s="1" t="n">
-        <v>0.0</v>
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>42</v>
@@ -4903,7 +5266,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>40</v>
       </c>
@@ -4916,17 +5279,17 @@
       <c r="D151" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E151" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F151" s="1" t="n">
-        <v>62.0</v>
-      </c>
-      <c r="G151" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H151" s="1" t="n">
-        <v>0.0</v>
+      <c r="E151" s="1">
+        <v>0</v>
+      </c>
+      <c r="F151" s="1">
+        <v>62</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>42</v>
@@ -4935,7 +5298,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>26</v>
       </c>
@@ -4948,17 +5311,17 @@
       <c r="D152" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E152" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F152" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G152" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H152" s="1" t="n">
-        <v>0.0</v>
+      <c r="E152" s="1">
+        <v>0</v>
+      </c>
+      <c r="F152" s="1">
+        <v>1</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>42</v>
@@ -4967,7 +5330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>23</v>
       </c>
@@ -4980,17 +5343,17 @@
       <c r="D153" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E153" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F153" s="1" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G153" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H153" s="1" t="n">
-        <v>0.0</v>
+      <c r="E153" s="1">
+        <v>0</v>
+      </c>
+      <c r="F153" s="1">
+        <v>2</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>42</v>
@@ -4999,7 +5362,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>15</v>
       </c>
@@ -5012,17 +5375,17 @@
       <c r="D154" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E154" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F154" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G154" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H154" s="1" t="n">
-        <v>0.0</v>
+      <c r="E154" s="1">
+        <v>0</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>42</v>
@@ -5031,7 +5394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>15</v>
       </c>
@@ -5044,17 +5407,17 @@
       <c r="D155" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E155" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F155" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G155" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H155" s="1" t="n">
-        <v>0.0</v>
+      <c r="E155" s="1">
+        <v>0</v>
+      </c>
+      <c r="F155" s="1">
+        <v>3</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+      <c r="H155" s="1">
+        <v>0</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>42</v>
@@ -5063,7 +5426,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>26</v>
       </c>
@@ -5076,17 +5439,17 @@
       <c r="D156" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E156" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F156" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G156" s="1" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H156" s="1" t="n">
-        <v>0.0</v>
+      <c r="E156" s="1">
+        <v>0</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1</v>
+      </c>
+      <c r="G156" s="1">
+        <v>0</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>42</v>
@@ -5096,6 +5459,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>